--- a/output/laminas_comunales/comunal_i_peringr_median_a_2021_valparaiso.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2021_valparaiso.xlsx
@@ -1092,7 +1092,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1101,20 +1101,12 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Algarrobo</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>14.49</v>
+          <t>Rinconada</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1123,45 +1115,33 @@
           <t>Cabildo</t>
         </is>
       </c>
-      <c r="B3">
-        <v>18.75</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Calera</t>
+          <t>Petorca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Calle Larga</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>15.18</v>
+          <t>Panquehue</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cartagena</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>16.28</v>
+          <t>Olmué</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Casablanca</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>14.51</v>
+          <t>Cartagena</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1170,145 +1150,103 @@
           <t>Catemu</t>
         </is>
       </c>
-      <c r="B8">
-        <v>18.13</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Concón</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>12.4</v>
+          <t>Llaillay</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>El Quisco</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>18.21</v>
+          <t>San Felipe</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>El Tabo</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>15.93</v>
+          <t>Santa María</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hijuelas</t>
-        </is>
-      </c>
-      <c r="B12">
-        <v>16.71</v>
+          <t>Villa Alemana</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>La Cruz</t>
-        </is>
-      </c>
-      <c r="B13">
-        <v>13.54</v>
+          <t>Santo Domingo</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>La Ligua</t>
-        </is>
-      </c>
-      <c r="B14">
-        <v>19.2</v>
+          <t>San Antonio</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Limache</t>
-        </is>
-      </c>
-      <c r="B15">
-        <v>19.52</v>
+          <t>El Tabo</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Llaillay</t>
+          <t>El Quisco</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Los Andes</t>
-        </is>
-      </c>
-      <c r="B17">
-        <v>14.47</v>
+          <t>Algarrobo</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Nogales</t>
-        </is>
-      </c>
-      <c r="B18">
-        <v>14.37</v>
+          <t>Casablanca</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Olmué</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>22.08</v>
+          <t>Valparaíso</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Panquehue</t>
-        </is>
-      </c>
-      <c r="B20">
-        <v>19.32</v>
+          <t>Viña del Mar</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Papudo</t>
-        </is>
-      </c>
-      <c r="B21">
-        <v>14.8</v>
+          <t>Concón</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Petorca</t>
-        </is>
-      </c>
-      <c r="B22">
-        <v>24.23</v>
+          <t>Quintero</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1317,148 +1255,103 @@
           <t>Puchuncaví</t>
         </is>
       </c>
-      <c r="B23">
-        <v>15.55</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Putaendo</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>21.29</v>
+          <t>Zapallar</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Quillota</t>
-        </is>
-      </c>
-      <c r="B25">
-        <v>16.71</v>
+          <t>Papudo</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Quilpué</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>14.67</v>
+          <t>La Ligua</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Quintero</t>
-        </is>
-      </c>
-      <c r="B27">
-        <v>13.53</v>
+          <t>Limache</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rinconada</t>
-        </is>
-      </c>
-      <c r="B28">
-        <v>18.97</v>
+          <t>Quillota</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>15.97</v>
+          <t>Calera</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>San Esteban</t>
-        </is>
-      </c>
-      <c r="B30">
-        <v>14.92</v>
+          <t>Nogales</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>San Felipe</t>
-        </is>
-      </c>
-      <c r="B31">
-        <v>20</v>
+          <t>Calle Larga</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Santa María</t>
-        </is>
-      </c>
-      <c r="B32">
-        <v>20.36</v>
+          <t>La Cruz</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Santo Domingo</t>
-        </is>
-      </c>
-      <c r="B33">
-        <v>13.9</v>
+          <t>Putaendo</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>15.91</v>
+          <t>San Esteban</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Villa Alemana</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>15.08</v>
+          <t>Los Andes</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Viña del Mar</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>15.28</v>
+          <t>Hijuelas</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zapallar</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>17.49</v>
+          <t>Quilpué</t>
+        </is>
       </c>
     </row>
   </sheetData>
